--- a/docagent_clean_mvp/sample_data/raw_excels/SIG_SetA.xlsx
+++ b/docagent_clean_mvp/sample_data/raw_excels/SIG_SetA.xlsx
@@ -984,7 +984,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>User access rights are reviewed and re-certified on a quarterly basis by data owners.</t>
+          <t>Standard Access Control policy mandates that user access rights are reviewed and re-certified on a quarterly basis by data owners. [SIG-018]</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Compliant - Q2 2026 access review completed</t>
+          <t>Compliant - evidence on file</t>
         </is>
       </c>
     </row>
